--- a/sports_forms/007_martial_arts_course_registration_form--sports_forms.xlsx
+++ b/sports_forms/007_martial_arts_course_registration_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'white_belt'}</t>
+          <t>white_belt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'White Belt'}</t>
+          <t>White Belt</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'orange_belt'}</t>
+          <t>orange_belt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Orange Belt'}</t>
+          <t>Orange Belt</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'yellow_belt'}</t>
+          <t>yellow_belt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Yellow Belt'}</t>
+          <t>Yellow Belt</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'green_belt'}</t>
+          <t>green_belt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Green Belt'}</t>
+          <t>Green Belt</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'black_belt'}</t>
+          <t>black_belt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Black Belt'}</t>
+          <t>Black Belt</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'red_belt'}</t>
+          <t>red_belt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Red Belt'}</t>
+          <t>Red Belt</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'brown_belt'}</t>
+          <t>brown_belt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Brown Belt'}</t>
+          <t>Brown Belt</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'blue_belt'}</t>
+          <t>blue_belt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Blue Belt'}</t>
+          <t>Blue Belt</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'package_1'}</t>
+          <t>package_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Package 1'}</t>
+          <t>Package 1</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'package_2'}</t>
+          <t>package_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Package 2'}</t>
+          <t>Package 2</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'package_3'}</t>
+          <t>package_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Package 3'}</t>
+          <t>Package 3</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'package_a'}</t>
+          <t>package_a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Package A'}</t>
+          <t>Package A</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'package_b'}</t>
+          <t>package_b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Package B'}</t>
+          <t>Package B</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'package_c'}</t>
+          <t>package_c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Package C'}</t>
+          <t>Package C</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Card'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
